--- a/database.xlsx
+++ b/database.xlsx
@@ -579,18 +579,19 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JAC Motors Newspot</t>
+          <t>JAC Motors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -599,76 +600,76 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3</v>
-      </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -680,6 +681,7 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>JAC Motors</t>
@@ -781,6 +783,7 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>JAC Motors</t>
@@ -788,7 +791,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -858,19 +861,19 @@
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -882,6 +885,7 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>JAC Motors</t>
@@ -889,7 +893,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -956,19 +960,19 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -983,90 +987,91 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JAC Motors Newspot</t>
+          <t>JAC Motors</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1084,18 +1089,19 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JAC Motors Newspot</t>
+          <t>JAC Motors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1107,10 +1113,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1158,16 +1164,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1197,7 +1203,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1249,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1409,7 +1415,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1461,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1476,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z10" t="n">
         <v>1</v>
@@ -1485,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1515,7 +1521,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1582,16 +1588,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1621,11 +1627,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1673,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1688,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1727,11 +1733,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1779,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1797,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1833,7 +1839,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1885,10 +1891,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1900,16 +1906,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2045,11 +2051,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2067,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2097,10 +2103,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2112,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2151,7 +2157,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2218,16 +2224,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="n">
         <v>2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2257,11 +2263,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -2279,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2324,16 +2330,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2363,7 +2369,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2433,13 +2439,13 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2469,11 +2475,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2497,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2536,19 +2542,19 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -2681,11 +2687,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2706,13 +2712,13 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2748,19 +2754,19 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
         <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -2787,11 +2793,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -2854,16 +2860,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -2872,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
@@ -2893,11 +2899,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -2906,10 +2912,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2918,13 +2924,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2960,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
         <v>6</v>
       </c>
       <c r="AA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -2999,7 +3005,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3012,10 +3018,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3024,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3066,16 +3072,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3084,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
@@ -3105,11 +3111,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -3175,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3211,11 +3217,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -3281,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3317,11 +3323,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -3330,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3354,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3369,10 +3375,10 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3387,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -3529,11 +3535,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -3542,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -3584,10 +3590,10 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -3596,16 +3602,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -3635,11 +3641,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -3672,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3705,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -3741,7 +3747,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -3754,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3793,13 +3799,13 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3808,16 +3814,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -3847,7 +3853,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -3860,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3917,13 +3923,13 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -3953,11 +3959,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -4005,10 +4011,10 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -4020,16 +4026,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4059,11 +4065,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -4111,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4126,16 +4132,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4271,11 +4277,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -4320,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -4377,11 +4383,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -4426,7 +4432,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -4589,14 +4595,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -4659,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -4801,14 +4807,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -4871,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -4907,7 +4913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -4977,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -5119,7 +5125,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -5186,10 +5192,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -5204,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -5225,7 +5231,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5280,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -5295,22 +5301,22 @@
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
@@ -5331,7 +5337,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -5386,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -5398,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -5407,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -5437,14 +5443,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -5489,7 +5495,7 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -5507,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -5543,14 +5549,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -5595,7 +5601,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5613,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -5649,7 +5655,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -5701,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5716,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -5755,7 +5761,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -5807,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5822,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -5967,11 +5973,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -5980,70 +5986,70 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>15</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
         <v>2</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>5</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6179,75 +6185,75 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>16</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
         <v>2</v>
       </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>15</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1</v>
-      </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
@@ -6255,7 +6261,7 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -6285,11 +6291,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -6301,7 +6307,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -6322,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -6352,13 +6358,13 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
@@ -6709,14 +6715,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -6776,10 +6782,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -6921,14 +6927,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -6991,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -7027,11 +7033,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -7094,16 +7100,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7112,7 +7118,7 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
@@ -7133,20 +7139,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -7203,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -7239,20 +7245,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -7309,13 +7315,13 @@
         <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -7324,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
@@ -7345,7 +7351,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -7415,7 +7421,7 @@
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -7557,11 +7563,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -7609,7 +7615,7 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -7618,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
         <v>0</v>
@@ -7663,7 +7669,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -7724,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" t="n">
         <v>0</v>
@@ -7733,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -7769,14 +7775,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -7821,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -7839,7 +7845,7 @@
         <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -7875,14 +7881,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -7945,13 +7951,13 @@
         <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -7981,7 +7987,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -8193,14 +8199,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -8263,7 +8269,7 @@
         <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -8299,11 +8305,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -8369,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -8405,20 +8411,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D76" t="n">
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -8475,7 +8481,7 @@
         <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -8511,7 +8517,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -8524,7 +8530,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -8581,7 +8587,7 @@
         <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -8617,14 +8623,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -8657,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -8684,19 +8690,19 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
         <v>3</v>
       </c>
-      <c r="Z78" t="n">
-        <v>0</v>
-      </c>
       <c r="AA78" t="n">
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -8829,86 +8835,86 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
         <v>2</v>
       </c>
-      <c r="E80" t="n">
+      <c r="Z80" t="n">
         <v>2</v>
       </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>3</v>
-      </c>
       <c r="AA80" t="n">
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -8935,7 +8941,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -9002,16 +9008,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -9041,7 +9047,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -9102,25 +9108,25 @@
         <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X82" t="n">
         <v>0</v>
       </c>
       <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB82" t="n">
         <v>2</v>
       </c>
-      <c r="Z82" t="n">
+      <c r="AC82" t="n">
         <v>2</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -9147,7 +9153,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -9208,25 +9214,25 @@
         <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -9253,7 +9259,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -9320,16 +9326,16 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -9465,7 +9471,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -9478,7 +9484,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -9487,7 +9493,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -9532,22 +9538,22 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z86" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -9571,11 +9577,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -9638,16 +9644,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -9677,20 +9683,20 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -9699,7 +9705,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -9714,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
@@ -9741,25 +9747,25 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y88" t="n">
         <v>4</v>
       </c>
       <c r="Z88" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -9783,14 +9789,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -9820,7 +9826,7 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
@@ -9847,22 +9853,22 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -9889,11 +9895,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -9959,7 +9965,7 @@
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -9995,11 +10001,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -10065,7 +10071,7 @@
         <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -10101,7 +10107,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -10171,7 +10177,7 @@
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -10207,7 +10213,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -10277,7 +10283,7 @@
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -10419,20 +10425,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -10444,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -10474,7 +10480,7 @@
         <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -10486,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -10525,20 +10531,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -10550,7 +10556,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -10580,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -10592,7 +10598,7 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -10843,11 +10849,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -10856,7 +10862,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -10895,7 +10901,7 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -11055,11 +11061,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -11068,7 +11074,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -11107,7 +11113,7 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -11267,11 +11273,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -11319,7 +11325,7 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -11337,13 +11343,13 @@
         <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -11479,11 +11485,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -11531,7 +11537,7 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -11555,7 +11561,7 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -11585,7 +11591,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -11655,7 +11661,7 @@
         <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -11691,7 +11697,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -11704,7 +11710,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -11761,7 +11767,7 @@
         <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -11903,7 +11909,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -11916,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -11970,7 +11976,7 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z109" t="n">
         <v>0</v>
@@ -12009,7 +12015,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -12079,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -12115,7 +12121,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -12185,7 +12191,7 @@
         <v>1</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -12221,7 +12227,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -12288,7 +12294,7 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
         <v>1</v>
@@ -12327,7 +12333,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -12358,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
@@ -12379,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -12391,19 +12397,19 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -12539,14 +12545,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -12585,7 +12591,7 @@
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -12609,7 +12615,7 @@
         <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -12645,7 +12651,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -12676,7 +12682,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N116" t="n">
         <v>0</v>
@@ -12709,19 +12715,19 @@
         <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -12730,7 +12736,7 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="inlineStr">
         <is>
@@ -12751,14 +12757,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -12797,13 +12803,13 @@
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -12821,7 +12827,7 @@
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -12857,84 +12863,84 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" t="n">
         <v>2</v>
       </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>0</v>
-      </c>
       <c r="AC118" t="n">
         <v>0</v>
       </c>
@@ -12942,7 +12948,7 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF118" t="inlineStr">
         <is>
@@ -12963,14 +12969,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -13018,7 +13024,7 @@
         <v>0</v>
       </c>
       <c r="U119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -13069,14 +13075,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -13124,7 +13130,7 @@
         <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -13175,7 +13181,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -13242,10 +13248,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -13260,7 +13266,7 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF121" t="inlineStr">
         <is>
@@ -13387,7 +13393,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -13454,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -13493,7 +13499,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -13560,7 +13566,7 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z124" t="n">
         <v>0</v>
@@ -13569,7 +13575,7 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -13599,7 +13605,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -13666,16 +13672,16 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -13684,7 +13690,7 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="inlineStr">
         <is>
@@ -13705,7 +13711,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -13772,16 +13778,16 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
         <v>2</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>1</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -13806,12 +13812,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://keystarjacmotors.com.au/</t>
+          <t>Rothwell</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -13863,7 +13869,7 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -13900,7 +13906,7 @@
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -13912,12 +13918,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://keystarjacmotors.com.au/</t>
+          <t>Rothwell</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -13969,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -14006,7 +14012,7 @@
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -14018,7 +14024,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://keystarjacmotors.com.au/</t>
+          <t>Rothwell</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14112,7 +14118,7 @@
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -14124,7 +14130,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://keystarjacmotors.com.au/</t>
+          <t>Rothwell</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14218,7 +14224,7 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -14235,14 +14241,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -14290,7 +14296,7 @@
         <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -14302,10 +14308,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -14341,14 +14347,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -14396,7 +14402,7 @@
         <v>0</v>
       </c>
       <c r="U132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -14408,10 +14414,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z132" t="n">
         <v>2</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>1</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -14447,11 +14453,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -14514,13 +14520,13 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
         <v>0</v>
@@ -14553,83 +14559,83 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" t="n">
         <v>2</v>
       </c>
-      <c r="E134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>1</v>
-      </c>
       <c r="Z134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" t="n">
         <v>2</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -14659,7 +14665,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -14726,16 +14732,16 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA135" t="n">
         <v>1</v>
       </c>
       <c r="AB135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -14765,11 +14771,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
@@ -14832,10 +14838,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -14977,77 +14983,77 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z138" t="n">
         <v>2</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>1</v>
       </c>
       <c r="AA138" t="n">
         <v>0</v>
@@ -15083,7 +15089,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -15150,7 +15156,7 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
         <v>2</v>
@@ -15295,14 +15301,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -15347,7 +15353,7 @@
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -15362,10 +15368,10 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA141" t="n">
         <v>0</v>
@@ -15507,14 +15513,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -15577,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -15613,11 +15619,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
@@ -15665,7 +15671,7 @@
         <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -15680,10 +15686,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z144" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -15719,11 +15725,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -15768,7 +15774,7 @@
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T145" t="n">
         <v>0</v>
@@ -15780,22 +15786,22 @@
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X145" t="n">
         <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA145" t="n">
         <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -15931,11 +15937,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -15998,19 +16004,19 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z147" t="n">
         <v>2</v>
       </c>
-      <c r="Z147" t="n">
-        <v>1</v>
-      </c>
       <c r="AA147" t="n">
         <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD147" t="n">
         <v>0</v>
@@ -16037,11 +16043,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -16086,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148" t="n">
         <v>0</v>
@@ -16098,13 +16104,13 @@
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
         <v>0</v>
@@ -16143,7 +16149,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -16207,22 +16213,22 @@
         <v>0</v>
       </c>
       <c r="X149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y149" t="n">
         <v>1</v>
       </c>
       <c r="Z149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA149" t="n">
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD149" t="n">
         <v>0</v>
@@ -16249,7 +16255,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -16313,7 +16319,7 @@
         <v>0</v>
       </c>
       <c r="X150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y150" t="n">
         <v>1</v>
@@ -16355,11 +16361,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -16368,7 +16374,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -16386,7 +16392,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N151" t="n">
         <v>0</v>
@@ -16404,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
         <v>0</v>
@@ -16425,7 +16431,7 @@
         <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA151" t="n">
         <v>0</v>
@@ -16567,15 +16573,15 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
         <v>2</v>
       </c>
-      <c r="E153" t="n">
-        <v>0</v>
-      </c>
       <c r="F153" t="n">
         <v>0</v>
       </c>
@@ -16598,10 +16604,10 @@
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -16637,7 +16643,7 @@
         <v>0</v>
       </c>
       <c r="Z153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA153" t="n">
         <v>0</v>
@@ -16673,20 +16679,20 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -16707,7 +16713,7 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -16722,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T154" t="n">
         <v>0</v>
@@ -17097,7 +17103,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -17149,10 +17155,10 @@
         <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -17164,7 +17170,7 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
         <v>0</v>
@@ -17173,7 +17179,7 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -17309,11 +17315,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -17361,10 +17367,10 @@
         <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -17376,7 +17382,7 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z160" t="n">
         <v>0</v>
@@ -17415,11 +17421,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -17491,7 +17497,7 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -17627,11 +17633,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -17664,7 +17670,7 @@
         <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P163" t="n">
         <v>0</v>
@@ -17697,7 +17703,7 @@
         <v>0</v>
       </c>
       <c r="Z163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA163" t="n">
         <v>0</v>
@@ -17839,11 +17845,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -17876,7 +17882,7 @@
         <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P165" t="n">
         <v>0</v>
@@ -17909,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="Z165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA165" t="n">
         <v>0</v>
@@ -18051,7 +18057,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -18103,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U167" t="n">
         <v>0</v>
@@ -18118,7 +18124,7 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z167" t="n">
         <v>0</v>
@@ -18127,7 +18133,7 @@
         <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -18157,7 +18163,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -18209,7 +18215,7 @@
         <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U168" t="n">
         <v>0</v>
@@ -18224,7 +18230,7 @@
         <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z168" t="n">
         <v>0</v>
@@ -18233,7 +18239,7 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -18369,11 +18375,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -18439,7 +18445,7 @@
         <v>0</v>
       </c>
       <c r="Z170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA170" t="n">
         <v>0</v>
@@ -18475,11 +18481,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -18545,7 +18551,7 @@
         <v>0</v>
       </c>
       <c r="Z171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA171" t="n">
         <v>0</v>
@@ -18581,7 +18587,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -18793,7 +18799,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -18863,13 +18869,13 @@
         <v>0</v>
       </c>
       <c r="Z174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA174" t="n">
         <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -18899,7 +18905,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -18969,13 +18975,13 @@
         <v>0</v>
       </c>
       <c r="Z175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA175" t="n">
         <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC175" t="n">
         <v>0</v>
@@ -19005,14 +19011,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
@@ -19042,7 +19048,7 @@
         <v>0</v>
       </c>
       <c r="O176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P176" t="n">
         <v>0</v>
@@ -19075,7 +19081,7 @@
         <v>0</v>
       </c>
       <c r="Z176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA176" t="n">
         <v>0</v>
@@ -19111,14 +19117,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D177" t="n">
         <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -19181,7 +19187,7 @@
         <v>0</v>
       </c>
       <c r="Z177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA177" t="n">
         <v>0</v>
@@ -19217,11 +19223,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -19254,7 +19260,7 @@
         <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P178" t="n">
         <v>0</v>
@@ -19287,7 +19293,7 @@
         <v>0</v>
       </c>
       <c r="Z178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA178" t="n">
         <v>0</v>
@@ -19429,7 +19435,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -19496,10 +19502,10 @@
         <v>0</v>
       </c>
       <c r="Y180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA180" t="n">
         <v>0</v>
@@ -19641,14 +19647,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D182" t="n">
         <v>0</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -19708,10 +19714,10 @@
         <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -19747,7 +19753,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -19817,13 +19823,13 @@
         <v>0</v>
       </c>
       <c r="Z183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA183" t="n">
         <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -19853,14 +19859,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D184" t="n">
         <v>0</v>
       </c>
       <c r="E184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
@@ -19905,7 +19911,7 @@
         <v>0</v>
       </c>
       <c r="T184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U184" t="n">
         <v>0</v>
@@ -19920,7 +19926,7 @@
         <v>0</v>
       </c>
       <c r="Y184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z184" t="n">
         <v>1</v>
@@ -19959,7 +19965,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -20011,7 +20017,7 @@
         <v>0</v>
       </c>
       <c r="T185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U185" t="n">
         <v>0</v>
@@ -20026,16 +20032,16 @@
         <v>0</v>
       </c>
       <c r="Y185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA185" t="n">
         <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -20065,7 +20071,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -20117,7 +20123,7 @@
         <v>0</v>
       </c>
       <c r="T186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U186" t="n">
         <v>0</v>
@@ -20135,10 +20141,10 @@
         <v>0</v>
       </c>
       <c r="Z186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB186" t="n">
         <v>0</v>
@@ -20277,7 +20283,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -20329,7 +20335,7 @@
         <v>0</v>
       </c>
       <c r="T188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U188" t="n">
         <v>0</v>
@@ -20344,19 +20350,19 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z188" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD188" t="n">
         <v>0</v>
@@ -20383,7 +20389,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -20450,19 +20456,19 @@
         <v>0</v>
       </c>
       <c r="Y189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z189" t="n">
         <v>2</v>
       </c>
-      <c r="Z189" t="n">
-        <v>4</v>
-      </c>
       <c r="AA189" t="n">
         <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD189" t="n">
         <v>0</v>
@@ -20489,14 +20495,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
@@ -20541,7 +20547,7 @@
         <v>0</v>
       </c>
       <c r="T190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U190" t="n">
         <v>0</v>
@@ -20559,7 +20565,7 @@
         <v>0</v>
       </c>
       <c r="Z190" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA190" t="n">
         <v>0</v>
@@ -20701,11 +20707,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
@@ -20753,7 +20759,7 @@
         <v>0</v>
       </c>
       <c r="T192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U192" t="n">
         <v>0</v>
@@ -20771,13 +20777,13 @@
         <v>0</v>
       </c>
       <c r="Z192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA192" t="n">
         <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -20807,14 +20813,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D193" t="n">
         <v>2</v>
       </c>
       <c r="E193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -20877,13 +20883,13 @@
         <v>0</v>
       </c>
       <c r="Z193" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB193" t="n">
         <v>2</v>
-      </c>
-      <c r="AA193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB193" t="n">
-        <v>0</v>
       </c>
       <c r="AC193" t="n">
         <v>0</v>
@@ -21019,7 +21025,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -21086,13 +21092,13 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB195" t="n">
         <v>0</v>
@@ -21231,11 +21237,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
@@ -21298,16 +21304,16 @@
         <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -21337,11 +21343,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
@@ -21350,7 +21356,7 @@
         <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -21404,7 +21410,7 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z198" t="n">
         <v>1</v>
@@ -21443,11 +21449,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E199" t="n">
         <v>0</v>
@@ -21459,10 +21465,10 @@
         <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -21510,16 +21516,16 @@
         <v>0</v>
       </c>
       <c r="Y199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA199" t="n">
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -21549,7 +21555,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -21619,7 +21625,7 @@
         <v>0</v>
       </c>
       <c r="Z200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA200" t="n">
         <v>0</v>
@@ -21655,11 +21661,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
@@ -21707,7 +21713,7 @@
         <v>0</v>
       </c>
       <c r="T201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U201" t="n">
         <v>0</v>
@@ -21722,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="Y201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA201" t="n">
         <v>0</v>
@@ -21867,11 +21873,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
@@ -21880,7 +21886,7 @@
         <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -21904,7 +21910,7 @@
         <v>0</v>
       </c>
       <c r="O203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P203" t="n">
         <v>0</v>
@@ -21919,7 +21925,7 @@
         <v>0</v>
       </c>
       <c r="T203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U203" t="n">
         <v>0</v>
@@ -21934,7 +21940,7 @@
         <v>0</v>
       </c>
       <c r="Y203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z203" t="n">
         <v>0</v>
@@ -21973,7 +21979,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -21986,7 +21992,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -22010,7 +22016,7 @@
         <v>0</v>
       </c>
       <c r="O204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P204" t="n">
         <v>0</v>
@@ -22043,7 +22049,7 @@
         <v>0</v>
       </c>
       <c r="Z204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA204" t="n">
         <v>0</v>
@@ -22079,11 +22085,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
@@ -22149,13 +22155,13 @@
         <v>0</v>
       </c>
       <c r="Z205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA205" t="n">
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -22291,11 +22297,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
@@ -22343,7 +22349,7 @@
         <v>0</v>
       </c>
       <c r="T207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U207" t="n">
         <v>0</v>
@@ -22358,10 +22364,10 @@
         <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA207" t="n">
         <v>0</v>
@@ -22397,11 +22403,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
@@ -22467,13 +22473,13 @@
         <v>0</v>
       </c>
       <c r="Z208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA208" t="n">
         <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -22482,7 +22488,7 @@
         <v>0</v>
       </c>
       <c r="AE208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF208" t="inlineStr">
         <is>
@@ -22503,7 +22509,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -22555,31 +22561,31 @@
         <v>0</v>
       </c>
       <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" t="n">
+        <v>0</v>
+      </c>
+      <c r="W209" t="n">
+        <v>0</v>
+      </c>
+      <c r="X209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y209" t="n">
         <v>2</v>
       </c>
-      <c r="U209" t="n">
-        <v>0</v>
-      </c>
-      <c r="V209" t="n">
-        <v>0</v>
-      </c>
-      <c r="W209" t="n">
-        <v>0</v>
-      </c>
-      <c r="X209" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y209" t="n">
-        <v>1</v>
-      </c>
       <c r="Z209" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB209" t="n">
         <v>2</v>
-      </c>
-      <c r="AA209" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB209" t="n">
-        <v>0</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -22609,7 +22615,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -22676,10 +22682,10 @@
         <v>0</v>
       </c>
       <c r="Y210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z210" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AA210" t="n">
         <v>0</v>
@@ -22694,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="AE210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF210" t="inlineStr">
         <is>
@@ -22715,11 +22721,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E211" t="n">
         <v>1</v>
@@ -22770,7 +22776,7 @@
         <v>0</v>
       </c>
       <c r="U211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V211" t="n">
         <v>0</v>
@@ -22782,10 +22788,10 @@
         <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA211" t="n">
         <v>0</v>
@@ -22821,77 +22827,77 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0</v>
+      </c>
+      <c r="V212" t="n">
+        <v>0</v>
+      </c>
+      <c r="W212" t="n">
+        <v>0</v>
+      </c>
+      <c r="X212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z212" t="n">
         <v>2</v>
-      </c>
-      <c r="E212" t="n">
-        <v>1</v>
-      </c>
-      <c r="F212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H212" t="n">
-        <v>0</v>
-      </c>
-      <c r="I212" t="n">
-        <v>0</v>
-      </c>
-      <c r="J212" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L212" t="n">
-        <v>0</v>
-      </c>
-      <c r="M212" t="n">
-        <v>0</v>
-      </c>
-      <c r="N212" t="n">
-        <v>0</v>
-      </c>
-      <c r="O212" t="n">
-        <v>0</v>
-      </c>
-      <c r="P212" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" t="n">
-        <v>0</v>
-      </c>
-      <c r="T212" t="n">
-        <v>0</v>
-      </c>
-      <c r="U212" t="n">
-        <v>2</v>
-      </c>
-      <c r="V212" t="n">
-        <v>0</v>
-      </c>
-      <c r="W212" t="n">
-        <v>0</v>
-      </c>
-      <c r="X212" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y212" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z212" t="n">
-        <v>0</v>
       </c>
       <c r="AA212" t="n">
         <v>0</v>
@@ -22927,7 +22933,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -22994,10 +23000,10 @@
         <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z213" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA213" t="n">
         <v>0</v>
@@ -23033,7 +23039,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -23100,10 +23106,10 @@
         <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z214" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA214" t="n">
         <v>0</v>
@@ -23139,11 +23145,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E215" t="n">
         <v>0</v>
@@ -23152,7 +23158,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -23206,7 +23212,7 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z215" t="n">
         <v>1</v>
@@ -23351,11 +23357,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
@@ -23418,7 +23424,7 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z217" t="n">
         <v>1</v>
@@ -23457,11 +23463,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E218" t="n">
         <v>0</v>
@@ -23470,7 +23476,7 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -23669,14 +23675,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D220" t="n">
         <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
@@ -23721,7 +23727,7 @@
         <v>0</v>
       </c>
       <c r="T220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U220" t="n">
         <v>0</v>
@@ -23730,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="W220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X220" t="n">
         <v>0</v>
@@ -23745,7 +23751,7 @@
         <v>0</v>
       </c>
       <c r="AB220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC220" t="n">
         <v>0</v>
@@ -23775,14 +23781,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
@@ -23827,7 +23833,7 @@
         <v>0</v>
       </c>
       <c r="T221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U221" t="n">
         <v>0</v>
@@ -23836,7 +23842,7 @@
         <v>0</v>
       </c>
       <c r="W221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X221" t="n">
         <v>0</v>
@@ -23881,7 +23887,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -23951,13 +23957,13 @@
         <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -23987,11 +23993,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E223" t="n">
         <v>0</v>
@@ -24057,7 +24063,7 @@
         <v>0</v>
       </c>
       <c r="Z223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -24093,7 +24099,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D224" t="n">

--- a/database.xlsx
+++ b/database.xlsx
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -21258,7 +21258,7 @@
       </c>
       <c r="AF200" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="AF201" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -21466,7 +21466,7 @@
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -21570,7 +21570,7 @@
       </c>
       <c r="AF203" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -21674,7 +21674,7 @@
       </c>
       <c r="AF204" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AF214" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -22818,7 +22818,7 @@
       </c>
       <c r="AF215" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -22922,7 +22922,7 @@
       </c>
       <c r="AF216" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -23026,7 +23026,7 @@
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF224"/>
+  <dimension ref="A1:AF220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17949,7 +17949,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
         <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U169" t="n">
         <v>0</v>
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -18157,7 +18157,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -18184,7 +18184,7 @@
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N171" t="n">
         <v>0</v>
@@ -18413,7 +18413,7 @@
         <v>0</v>
       </c>
       <c r="T173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U173" t="n">
         <v>0</v>
@@ -19184,11 +19184,11 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>140221</v>
+        <v>136301</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Rothwell</t>
+          <t>Shepparton</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -19197,7 +19197,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -19206,7 +19206,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -19245,7 +19245,7 @@
         <v>0</v>
       </c>
       <c r="T181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U181" t="n">
         <v>0</v>
@@ -19288,11 +19288,11 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>140221</v>
+        <v>136301</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Rothwell</t>
+          <t>Shepparton</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -19301,10 +19301,10 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -19367,7 +19367,7 @@
         <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -19392,11 +19392,11 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>140221</v>
+        <v>136301</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Rothwell</t>
+          <t>Shepparton</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -19405,7 +19405,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
@@ -19432,7 +19432,7 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
         <v>0</v>
       </c>
       <c r="Y183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z183" t="n">
         <v>0</v>
@@ -19496,16 +19496,16 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>140221</v>
+        <v>136301</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Rothwell</t>
+          <t>Shepparton</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -19557,7 +19557,7 @@
         <v>0</v>
       </c>
       <c r="T184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U184" t="n">
         <v>0</v>
@@ -19575,7 +19575,7 @@
         <v>0</v>
       </c>
       <c r="Z184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA184" t="n">
         <v>0</v>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -19622,7 +19622,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -19676,10 +19676,10 @@
         <v>0</v>
       </c>
       <c r="Y185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA185" t="n">
         <v>0</v>
@@ -19713,14 +19713,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
@@ -19783,7 +19783,7 @@
         <v>0</v>
       </c>
       <c r="Z186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA186" t="n">
         <v>0</v>
@@ -19808,20 +19808,20 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>136301</v>
+        <v>141271</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Shepparton</t>
+          <t>Springwood</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
@@ -19887,7 +19887,7 @@
         <v>1</v>
       </c>
       <c r="Z187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA187" t="n">
         <v>0</v>
@@ -19912,20 +19912,20 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>136301</v>
+        <v>141271</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Shepparton</t>
+          <t>Springwood</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
         <v>0</v>
       </c>
       <c r="T188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U188" t="n">
         <v>0</v>
@@ -19988,16 +19988,16 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z188" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA188" t="n">
         <v>0</v>
       </c>
       <c r="AB188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC188" t="n">
         <v>0</v>
@@ -20016,16 +20016,16 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>136301</v>
+        <v>141271</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Shepparton</t>
+          <t>Springwood</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="Z189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA189" t="n">
         <v>0</v>
@@ -20120,16 +20120,16 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>136301</v>
+        <v>141271</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Shepparton</t>
+          <t>Springwood</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -20199,7 +20199,7 @@
         <v>0</v>
       </c>
       <c r="Z190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA190" t="n">
         <v>0</v>
@@ -20233,11 +20233,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
@@ -20300,7 +20300,7 @@
         <v>0</v>
       </c>
       <c r="Y191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z191" t="n">
         <v>1</v>
@@ -20328,20 +20328,20 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>141271</v>
+        <v>123401</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Springwood</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
@@ -20389,7 +20389,7 @@
         <v>0</v>
       </c>
       <c r="T192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U192" t="n">
         <v>0</v>
@@ -20404,16 +20404,16 @@
         <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z192" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA192" t="n">
         <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -20432,16 +20432,16 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>141271</v>
+        <v>123401</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Springwood</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -20490,7 +20490,7 @@
         <v>0</v>
       </c>
       <c r="S193" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T193" t="n">
         <v>0</v>
@@ -20508,10 +20508,10 @@
         <v>0</v>
       </c>
       <c r="Y193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA193" t="n">
         <v>0</v>
@@ -20536,29 +20536,29 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>141271</v>
+        <v>123401</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Springwood</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D194" t="n">
         <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
         <v>0</v>
       </c>
       <c r="Z194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA194" t="n">
         <v>0</v>
@@ -20640,20 +20640,20 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>141271</v>
+        <v>143501</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Springwood</t>
+          <t>Toowoomba</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
@@ -20716,13 +20716,13 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB195" t="n">
         <v>0</v>
@@ -20738,17 +20738,17 @@
       </c>
       <c r="AF195" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>123401</v>
+        <v>143501</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Toowoomba</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -20757,7 +20757,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
@@ -20790,7 +20790,7 @@
         <v>0</v>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P196" t="n">
         <v>0</v>
@@ -20842,22 +20842,22 @@
       </c>
       <c r="AF196" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>123401</v>
+        <v>148141</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Townsville</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -20906,10 +20906,10 @@
         <v>0</v>
       </c>
       <c r="S197" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U197" t="n">
         <v>0</v>
@@ -20927,10 +20927,10 @@
         <v>0</v>
       </c>
       <c r="Z197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB197" t="n">
         <v>0</v>
@@ -20946,35 +20946,35 @@
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>123401</v>
+        <v>148141</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Townsville</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -21037,7 +21037,7 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -21050,22 +21050,22 @@
       </c>
       <c r="AF198" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>143501</v>
+        <v>148141</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Toowoomba</t>
+          <t>Townsville</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -21132,16 +21132,16 @@
         <v>0</v>
       </c>
       <c r="Y199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z199" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -21160,16 +21160,16 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>143501</v>
+        <v>148141</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Toowoomba</t>
+          <t>Townsville</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -21206,7 +21206,7 @@
         <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P200" t="n">
         <v>0</v>
@@ -21239,7 +21239,7 @@
         <v>0</v>
       </c>
       <c r="Z200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA200" t="n">
         <v>0</v>
@@ -21264,11 +21264,11 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>148141</v>
+        <v>122591</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Townsville</t>
+          <t>Tuggerah</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
@@ -21286,7 +21286,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -21328,7 +21328,7 @@
         <v>1</v>
       </c>
       <c r="U201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V201" t="n">
         <v>0</v>
@@ -21346,7 +21346,7 @@
         <v>1</v>
       </c>
       <c r="AA201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB201" t="n">
         <v>0</v>
@@ -21362,17 +21362,17 @@
       </c>
       <c r="AF201" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>148141</v>
+        <v>122591</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Townsville</t>
+          <t>Tuggerah</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -21381,7 +21381,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -21414,10 +21414,10 @@
         <v>0</v>
       </c>
       <c r="O202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q202" t="n">
         <v>0</v>
@@ -21447,13 +21447,13 @@
         <v>0</v>
       </c>
       <c r="Z202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA202" t="n">
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -21466,17 +21466,17 @@
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>148141</v>
+        <v>122591</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Townsville</t>
+          <t>Tuggerah</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -21533,13 +21533,13 @@
         <v>0</v>
       </c>
       <c r="T203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U203" t="n">
         <v>0</v>
       </c>
       <c r="V203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W203" t="n">
         <v>0</v>
@@ -21548,10 +21548,10 @@
         <v>0</v>
       </c>
       <c r="Y203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z203" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA203" t="n">
         <v>0</v>
@@ -21570,17 +21570,17 @@
       </c>
       <c r="AF203" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>148141</v>
+        <v>122591</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Townsville</t>
+          <t>Tuggerah</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -21589,7 +21589,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
@@ -21622,7 +21622,7 @@
         <v>0</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P204" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>0</v>
       </c>
       <c r="Z204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA204" t="n">
         <v>0</v>
@@ -21674,7 +21674,7 @@
       </c>
       <c r="AF204" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -21689,83 +21689,83 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="n">
+        <v>0</v>
+      </c>
+      <c r="T205" t="n">
+        <v>0</v>
+      </c>
+      <c r="U205" t="n">
+        <v>0</v>
+      </c>
+      <c r="V205" t="n">
+        <v>0</v>
+      </c>
+      <c r="W205" t="n">
+        <v>0</v>
+      </c>
+      <c r="X205" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB205" t="n">
         <v>2</v>
-      </c>
-      <c r="E205" t="n">
-        <v>0</v>
-      </c>
-      <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="n">
-        <v>1</v>
-      </c>
-      <c r="H205" t="n">
-        <v>0</v>
-      </c>
-      <c r="I205" t="n">
-        <v>0</v>
-      </c>
-      <c r="J205" t="n">
-        <v>0</v>
-      </c>
-      <c r="K205" t="n">
-        <v>0</v>
-      </c>
-      <c r="L205" t="n">
-        <v>0</v>
-      </c>
-      <c r="M205" t="n">
-        <v>0</v>
-      </c>
-      <c r="N205" t="n">
-        <v>0</v>
-      </c>
-      <c r="O205" t="n">
-        <v>0</v>
-      </c>
-      <c r="P205" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0</v>
-      </c>
-      <c r="S205" t="n">
-        <v>0</v>
-      </c>
-      <c r="T205" t="n">
-        <v>1</v>
-      </c>
-      <c r="U205" t="n">
-        <v>1</v>
-      </c>
-      <c r="V205" t="n">
-        <v>0</v>
-      </c>
-      <c r="W205" t="n">
-        <v>0</v>
-      </c>
-      <c r="X205" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y205" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z205" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB205" t="n">
-        <v>0</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -21793,7 +21793,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -21830,10 +21830,10 @@
         <v>0</v>
       </c>
       <c r="O206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q206" t="n">
         <v>0</v>
@@ -21869,7 +21869,7 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -21888,16 +21888,16 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122591</v>
+        <v>124861</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Tuggerah</t>
+          <t>Tweed Heads</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -21949,13 +21949,13 @@
         <v>0</v>
       </c>
       <c r="T207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U207" t="n">
         <v>0</v>
       </c>
       <c r="V207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W207" t="n">
         <v>0</v>
@@ -21964,16 +21964,16 @@
         <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA207" t="n">
         <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -21992,20 +21992,20 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122591</v>
+        <v>124861</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Tuggerah</t>
+          <t>Tweed Heads</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
@@ -22038,7 +22038,7 @@
         <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P208" t="n">
         <v>0</v>
@@ -22056,7 +22056,7 @@
         <v>0</v>
       </c>
       <c r="U208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V208" t="n">
         <v>0</v>
@@ -22077,7 +22077,7 @@
         <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -22096,16 +22096,16 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122591</v>
+        <v>124861</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Tuggerah</t>
+          <t>Tweed Heads</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -22118,7 +22118,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -22172,16 +22172,16 @@
         <v>0</v>
       </c>
       <c r="Y209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z209" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA209" t="n">
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -22200,16 +22200,16 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122591</v>
+        <v>126501</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Tuggerah</t>
+          <t>Wagga Wagga</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -22279,7 +22279,7 @@
         <v>0</v>
       </c>
       <c r="Z210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA210" t="n">
         <v>0</v>
@@ -22298,29 +22298,29 @@
       </c>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124861</v>
+        <v>126501</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Tweed Heads</t>
+          <t>Wagga Wagga</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D211" t="n">
         <v>0</v>
       </c>
       <c r="E211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
@@ -22383,7 +22383,7 @@
         <v>0</v>
       </c>
       <c r="Z211" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA211" t="n">
         <v>0</v>
@@ -22402,26 +22402,26 @@
       </c>
       <c r="AF211" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124861</v>
+        <v>132801</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Tweed Heads</t>
+          <t>Warrnambool</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
@@ -22472,7 +22472,7 @@
         <v>0</v>
       </c>
       <c r="U212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V212" t="n">
         <v>0</v>
@@ -22493,7 +22493,7 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -22512,20 +22512,20 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124861</v>
+        <v>132801</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Tweed Heads</t>
+          <t>Warrnambool</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E213" t="n">
         <v>0</v>
@@ -22588,10 +22588,10 @@
         <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA213" t="n">
         <v>0</v>
@@ -22616,20 +22616,20 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>126501</v>
+        <v>132801</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Wagga Wagga</t>
+          <t>Warrnambool</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E214" t="n">
         <v>0</v>
@@ -22695,7 +22695,7 @@
         <v>0</v>
       </c>
       <c r="Z214" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA214" t="n">
         <v>0</v>
@@ -22714,29 +22714,29 @@
       </c>
       <c r="AF214" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>126501</v>
+        <v>130291</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Wagga Wagga</t>
+          <t>Werribee</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
@@ -22769,7 +22769,7 @@
         <v>0</v>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q215" t="n">
         <v>0</v>
@@ -22799,13 +22799,13 @@
         <v>0</v>
       </c>
       <c r="Z215" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -22818,22 +22818,22 @@
       </c>
       <c r="AF215" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>132801</v>
+        <v>130291</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Warrnambool</t>
+          <t>Werribee</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -22885,7 +22885,7 @@
         <v>0</v>
       </c>
       <c r="T216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U216" t="n">
         <v>0</v>
@@ -22900,10 +22900,10 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA216" t="n">
         <v>0</v>
@@ -22928,20 +22928,20 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>132801</v>
+        <v>130291</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Warrnambool</t>
+          <t>Werribee</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
@@ -23004,16 +23004,16 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA217" t="n">
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -23032,20 +23032,20 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>132801</v>
+        <v>130291</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Warrnambool</t>
+          <t>Werribee</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
         <v>0</v>
@@ -23108,7 +23108,7 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z218" t="n">
         <v>0</v>
@@ -23117,7 +23117,7 @@
         <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -23145,83 +23145,83 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="n">
+        <v>0</v>
+      </c>
+      <c r="T219" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" t="n">
+        <v>0</v>
+      </c>
+      <c r="V219" t="n">
+        <v>0</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1</v>
+      </c>
+      <c r="X219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB219" t="n">
         <v>2</v>
-      </c>
-      <c r="E219" t="n">
-        <v>2</v>
-      </c>
-      <c r="F219" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" t="n">
-        <v>0</v>
-      </c>
-      <c r="H219" t="n">
-        <v>0</v>
-      </c>
-      <c r="I219" t="n">
-        <v>0</v>
-      </c>
-      <c r="J219" t="n">
-        <v>0</v>
-      </c>
-      <c r="K219" t="n">
-        <v>0</v>
-      </c>
-      <c r="L219" t="n">
-        <v>0</v>
-      </c>
-      <c r="M219" t="n">
-        <v>0</v>
-      </c>
-      <c r="N219" t="n">
-        <v>0</v>
-      </c>
-      <c r="O219" t="n">
-        <v>0</v>
-      </c>
-      <c r="P219" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" t="n">
-        <v>0</v>
-      </c>
-      <c r="T219" t="n">
-        <v>0</v>
-      </c>
-      <c r="U219" t="n">
-        <v>0</v>
-      </c>
-      <c r="V219" t="n">
-        <v>0</v>
-      </c>
-      <c r="W219" t="n">
-        <v>0</v>
-      </c>
-      <c r="X219" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y219" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z219" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA219" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB219" t="n">
-        <v>3</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -23249,11 +23249,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E220" t="n">
         <v>0</v>
@@ -23301,7 +23301,7 @@
         <v>0</v>
       </c>
       <c r="T220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U220" t="n">
         <v>0</v>
@@ -23319,7 +23319,7 @@
         <v>1</v>
       </c>
       <c r="Z220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA220" t="n">
         <v>0</v>
@@ -23337,422 +23337,6 @@
         <v>0</v>
       </c>
       <c r="AF220" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>130291</v>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Werribee</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>0</v>
-      </c>
-      <c r="E221" t="n">
-        <v>0</v>
-      </c>
-      <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="n">
-        <v>0</v>
-      </c>
-      <c r="H221" t="n">
-        <v>0</v>
-      </c>
-      <c r="I221" t="n">
-        <v>0</v>
-      </c>
-      <c r="J221" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" t="n">
-        <v>0</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0</v>
-      </c>
-      <c r="N221" t="n">
-        <v>0</v>
-      </c>
-      <c r="O221" t="n">
-        <v>0</v>
-      </c>
-      <c r="P221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
-      <c r="S221" t="n">
-        <v>0</v>
-      </c>
-      <c r="T221" t="n">
-        <v>0</v>
-      </c>
-      <c r="U221" t="n">
-        <v>0</v>
-      </c>
-      <c r="V221" t="n">
-        <v>0</v>
-      </c>
-      <c r="W221" t="n">
-        <v>0</v>
-      </c>
-      <c r="X221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y221" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z221" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA221" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB221" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC221" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD221" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE221" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
-        <v>130291</v>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Werribee</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>0</v>
-      </c>
-      <c r="E222" t="n">
-        <v>0</v>
-      </c>
-      <c r="F222" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" t="n">
-        <v>0</v>
-      </c>
-      <c r="H222" t="n">
-        <v>0</v>
-      </c>
-      <c r="I222" t="n">
-        <v>0</v>
-      </c>
-      <c r="J222" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" t="n">
-        <v>0</v>
-      </c>
-      <c r="N222" t="n">
-        <v>0</v>
-      </c>
-      <c r="O222" t="n">
-        <v>0</v>
-      </c>
-      <c r="P222" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="n">
-        <v>0</v>
-      </c>
-      <c r="T222" t="n">
-        <v>0</v>
-      </c>
-      <c r="U222" t="n">
-        <v>0</v>
-      </c>
-      <c r="V222" t="n">
-        <v>0</v>
-      </c>
-      <c r="W222" t="n">
-        <v>0</v>
-      </c>
-      <c r="X222" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y222" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z222" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA222" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB222" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC222" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD222" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE222" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>130291</v>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Werribee</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>0</v>
-      </c>
-      <c r="E223" t="n">
-        <v>0</v>
-      </c>
-      <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="n">
-        <v>0</v>
-      </c>
-      <c r="H223" t="n">
-        <v>0</v>
-      </c>
-      <c r="I223" t="n">
-        <v>0</v>
-      </c>
-      <c r="J223" t="n">
-        <v>0</v>
-      </c>
-      <c r="K223" t="n">
-        <v>0</v>
-      </c>
-      <c r="L223" t="n">
-        <v>0</v>
-      </c>
-      <c r="M223" t="n">
-        <v>0</v>
-      </c>
-      <c r="N223" t="n">
-        <v>0</v>
-      </c>
-      <c r="O223" t="n">
-        <v>0</v>
-      </c>
-      <c r="P223" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0</v>
-      </c>
-      <c r="S223" t="n">
-        <v>0</v>
-      </c>
-      <c r="T223" t="n">
-        <v>0</v>
-      </c>
-      <c r="U223" t="n">
-        <v>0</v>
-      </c>
-      <c r="V223" t="n">
-        <v>0</v>
-      </c>
-      <c r="W223" t="n">
-        <v>1</v>
-      </c>
-      <c r="X223" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y223" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z223" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA223" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB223" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC223" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD223" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE223" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF223" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>130291</v>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Werribee</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>0</v>
-      </c>
-      <c r="E224" t="n">
-        <v>0</v>
-      </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" t="n">
-        <v>0</v>
-      </c>
-      <c r="H224" t="n">
-        <v>0</v>
-      </c>
-      <c r="I224" t="n">
-        <v>0</v>
-      </c>
-      <c r="J224" t="n">
-        <v>0</v>
-      </c>
-      <c r="K224" t="n">
-        <v>0</v>
-      </c>
-      <c r="L224" t="n">
-        <v>0</v>
-      </c>
-      <c r="M224" t="n">
-        <v>0</v>
-      </c>
-      <c r="N224" t="n">
-        <v>0</v>
-      </c>
-      <c r="O224" t="n">
-        <v>0</v>
-      </c>
-      <c r="P224" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0</v>
-      </c>
-      <c r="S224" t="n">
-        <v>0</v>
-      </c>
-      <c r="T224" t="n">
-        <v>0</v>
-      </c>
-      <c r="U224" t="n">
-        <v>0</v>
-      </c>
-      <c r="V224" t="n">
-        <v>0</v>
-      </c>
-      <c r="W224" t="n">
-        <v>0</v>
-      </c>
-      <c r="X224" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y224" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z224" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA224" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB224" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC224" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD224" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE224" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF224" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
